--- a/test-files/hr.xlsx
+++ b/test-files/hr.xlsx
@@ -58,7 +58,7 @@
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -425,14 +425,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="27" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,94 +460,126 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Дата приёма</t>
+          <t>Дата трудоустройства</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>E-mail</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Стаж, лет</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Сидоров Алексей Николаевич</t>
+          <t>Сидорова Ольга Дмитриевна</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Разработчик</t>
+          <t>Руководитель отдела</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Продажи</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>224025</v>
+        <v>154524</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.12.2024</t>
-        </is>
+          <t>25.01.2019</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>sidorova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Иванова Анна Сергеевна</t>
+          <t>Волков Антон Игоревич</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Старший менеджер</t>
+          <t>Аналитик</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Разработка</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>226369</v>
-      </c>
+          <t>Дизайн</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>25.06.2021</t>
-        </is>
+          <t>17.01.2019</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>volkov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Лебедев Сергей Александрович</t>
+          <t>Смирнов Владимир Андреевич</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Старший аналитик</t>
+          <t>UX-исследователь</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Разработка</t>
+          <t>Маркетинг</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>56402</v>
+        <v>136414</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>09.07.2018</t>
-        </is>
+          <t>10.08.2022</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>smirnov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Лебедев Сергей Александрович</t>
+          <t>Волкова Полина Игоревна</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Бухгалтер</t>
+          <t>Менеджер</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -554,18 +588,26 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>69091</v>
+        <v>201497</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>09.02.2023</t>
-        </is>
+          <t>26.09.2019</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>volkova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Кузнецова Екатерина Игоревна</t>
+          <t>Волков Антон Игоревич</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -575,66 +617,210 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>Поддержка</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>100970</v>
+        <v>106539.77</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>22.04.2022</t>
-        </is>
+          <t>16.04.2024</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>volkov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Соколова Наталья Андреевна</t>
+          <t>Иванов Иван Иванович</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Дизайнер</t>
+          <t>Бухгалтер</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Разработка</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>88684</v>
-      </c>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>23.01.2018</t>
-        </is>
+          <t>19.06.2021</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ivanov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Смирнов Владимир Андреевич</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Бухгалтер</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>06.05.2018</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Петрова Мария Викторовна</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Дизайнер</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Поддержка</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>135035</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>13.05.2024</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>petrova@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Соколов Михаил Викторович</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Специалист по продажам</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Маркетинг</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>215484.67</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>16.12.2022</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>sokolov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Кузнецов Дмитрий Сергеевич</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Дизайнер</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Разработка</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>96107</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>23.10.2023</t>
-        </is>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Старший разработчик</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Аналитика</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>205486</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>17.06.2021</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Иванов Иван Иванович</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Старший аналитик</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>250320</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>05.09.2021</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ivanov@gigachat-corp.ru</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
